--- a/zy70609/test_data.xlsx
+++ b/zy70609/test_data.xlsx
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,6 +791,70 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>E006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-17 08:00:00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>东门闸机1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>E007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>未知人员</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-17 10:00:00</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>北门闸机</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>entry</t>
         </is>
       </c>
     </row>
